--- a/data/2024-25/AHLdelegacije - do konca master round.xlsx
+++ b/data/2024-25/AHLdelegacije - do konca master round.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977C86B8-53BB-4D1E-B283-92FACFC2557F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
+    <sheet name="AHL" sheetId="1" r:id="rId1"/>
+    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
+    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
+    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2954" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2950" uniqueCount="469">
   <si>
     <t>sl</t>
   </si>
@@ -494,9 +508,6 @@
   </si>
   <si>
     <t>2025-02-25</t>
-  </si>
-  <si>
-    <t>zbrisano</t>
   </si>
   <si>
     <t>HuberRe</t>
@@ -1432,53 +1443,53 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF9C0006"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF006100"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="36"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="36"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1490,25 +1501,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1520,7 +1531,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1537,7 +1548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1548,7 +1559,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1817,25 +1828,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1930,12 +1926,27 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1944,7 +1955,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.5999633777886288"/>
+          <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2223,9 +2234,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BQ73"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -2298,7 +2309,7 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
         <v>20</v>
@@ -2309,7 +2320,7 @@
       </c>
       <c r="C1">
         <f>COUNTIF(C4:C67,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D67,"&lt;&gt;")</f>
@@ -2333,7 +2344,7 @@
       </c>
       <c r="I1">
         <f>COUNTIF(I4:I68,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J1">
         <f>COUNTIF(J4:J64,"&lt;&gt;")</f>
@@ -2497,7 +2508,7 @@
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX65,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY1">
         <f>COUNTIF(AY4:AY60,"&lt;&gt;")</f>
@@ -2509,7 +2520,7 @@
       </c>
       <c r="BA1">
         <f>COUNTIF(BA4:BA69,"&lt;&gt;")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB68,"&lt;&gt;")</f>
@@ -2576,7 +2587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2785,7 +2796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2994,7 +3005,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -3203,7 +3214,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3403,7 +3414,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -3603,7 +3614,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -3800,7 +3811,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -3994,7 +4005,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>93</v>
       </c>
@@ -4188,7 +4199,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -4382,7 +4393,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -4576,7 +4587,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -4761,7 +4772,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -4943,7 +4954,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -5122,7 +5133,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>134</v>
       </c>
@@ -5292,7 +5303,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -5456,7 +5467,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>136</v>
       </c>
@@ -5614,7 +5625,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -5769,7 +5780,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>149</v>
       </c>
@@ -5918,7 +5929,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>152</v>
       </c>
@@ -6058,7 +6069,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
@@ -6165,7 +6176,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>142</v>
       </c>
@@ -6263,7 +6274,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>135</v>
       </c>
@@ -6340,10 +6351,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>159</v>
-      </c>
+    <row r="24" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
         <v>144</v>
       </c>
@@ -6399,7 +6407,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="9:54" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I25" t="s">
         <v>127</v>
       </c>
@@ -6443,10 +6451,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="9:54" x14ac:dyDescent="0.25">
-      <c r="I26" t="s">
-        <v>159</v>
-      </c>
+    <row r="26" spans="1:65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P26" t="s">
         <v>144</v>
       </c>
@@ -6465,9 +6470,6 @@
       <c r="AT26" t="s">
         <v>150</v>
       </c>
-      <c r="AX26" t="s">
-        <v>159</v>
-      </c>
       <c r="AZ26" t="s">
         <v>158</v>
       </c>
@@ -6478,7 +6480,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R27" t="s">
         <v>144</v>
       </c>
@@ -6498,25 +6500,22 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R28" t="s">
         <v>127</v>
       </c>
       <c r="S28" t="s">
         <v>144</v>
       </c>
-      <c r="BA28" t="s">
-        <v>159</v>
-      </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="18:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R29" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6565,14 +6564,14 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:CH42"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -6620,7 +6619,7 @@
     <col min="83" max="83" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -6880,7 +6879,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -7140,7 +7139,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7400,7 +7399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -7660,7 +7659,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -7920,12 +7919,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -7949,7 +7948,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -8102,7 +8101,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -8116,7 +8115,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -8284,7 +8283,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -8466,7 +8465,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -8648,7 +8647,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -8674,7 +8673,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -8800,7 +8799,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -8952,7 +8951,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -9104,7 +9103,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -9256,7 +9255,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -9396,7 +9395,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -9536,7 +9535,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -9676,7 +9675,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -9816,7 +9815,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -9917,7 +9916,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -10018,7 +10017,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -10119,7 +10118,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -10220,7 +10219,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -10261,7 +10260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -10302,7 +10301,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -10343,7 +10342,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -10384,11 +10383,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10404,10 +10403,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:CH14"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -10494,7 +10493,7 @@
     <col min="101" max="101" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -10754,900 +10753,900 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" t="s">
         <v>161</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>162</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>163</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>164</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>165</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>166</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>167</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>168</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>169</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>170</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>171</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>172</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>173</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>174</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>175</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>176</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>177</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>178</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>179</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>180</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>181</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>182</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>183</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>184</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>185</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>186</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>187</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>188</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>189</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>190</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>191</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>192</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>193</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>194</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>195</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>196</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>197</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>198</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>199</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>200</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
+        <v>188</v>
+      </c>
+      <c r="AQ4" t="s">
         <v>201</v>
       </c>
-      <c r="AP4" t="s">
-        <v>189</v>
-      </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>202</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>203</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>204</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>205</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>206</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>207</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>208</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>209</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>210</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>211</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>212</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>213</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>214</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>215</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF4" t="s">
         <v>216</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BG4" t="s">
         <v>217</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BH4" t="s">
         <v>218</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BI4" t="s">
         <v>219</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BJ4" t="s">
         <v>220</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
         <v>221</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>222</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BM4" t="s">
         <v>223</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BN4" t="s">
         <v>224</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BO4" t="s">
         <v>225</v>
       </c>
-      <c r="BO4" t="s">
+      <c r="BP4" t="s">
         <v>226</v>
       </c>
-      <c r="BP4" t="s">
+      <c r="BQ4" t="s">
         <v>227</v>
       </c>
-      <c r="BQ4" t="s">
+      <c r="BR4" t="s">
         <v>228</v>
       </c>
-      <c r="BR4" t="s">
+      <c r="BS4" t="s">
         <v>229</v>
       </c>
-      <c r="BS4" t="s">
+      <c r="BT4" t="s">
         <v>230</v>
       </c>
-      <c r="BT4" t="s">
+      <c r="BU4" t="s">
         <v>231</v>
       </c>
-      <c r="BU4" t="s">
+      <c r="BV4" t="s">
         <v>232</v>
       </c>
-      <c r="BV4" t="s">
+      <c r="BW4" t="s">
         <v>233</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="BX4" t="s">
         <v>234</v>
       </c>
-      <c r="BX4" t="s">
+      <c r="BY4" t="s">
         <v>235</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="BZ4" t="s">
         <v>236</v>
       </c>
-      <c r="BZ4" t="s">
+      <c r="CA4" t="s">
         <v>237</v>
       </c>
-      <c r="CA4" t="s">
+      <c r="CB4" t="s">
         <v>238</v>
       </c>
-      <c r="CB4" t="s">
+      <c r="CC4" t="s">
         <v>239</v>
       </c>
-      <c r="CC4" t="s">
+      <c r="CD4" t="s">
         <v>240</v>
       </c>
-      <c r="CD4" t="s">
+      <c r="CE4" t="s">
         <v>241</v>
       </c>
-      <c r="CE4" t="s">
+      <c r="CF4" t="s">
         <v>242</v>
       </c>
-      <c r="CF4" t="s">
+      <c r="CG4" t="s">
         <v>243</v>
       </c>
-      <c r="CG4" t="s">
+      <c r="CH4" t="s">
         <v>244</v>
       </c>
-      <c r="CH4" t="s">
+    </row>
+    <row r="5" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>245</v>
       </c>
+      <c r="D5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H5" t="s">
+        <v>249</v>
+      </c>
+      <c r="K5" t="s">
+        <v>250</v>
+      </c>
+      <c r="L5" t="s">
+        <v>251</v>
+      </c>
+      <c r="N5" t="s">
+        <v>252</v>
+      </c>
+      <c r="P5" t="s">
+        <v>253</v>
+      </c>
+      <c r="R5" t="s">
+        <v>254</v>
+      </c>
+      <c r="T5" t="s">
+        <v>255</v>
+      </c>
+      <c r="U5" t="s">
+        <v>256</v>
+      </c>
+      <c r="V5" t="s">
+        <v>257</v>
+      </c>
+      <c r="W5" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>259</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>260</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>263</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>264</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>265</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>266</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>267</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>268</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>269</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>270</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>272</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>273</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>274</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>275</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>276</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>277</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>278</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>279</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>280</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>281</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>282</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>283</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>284</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>285</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>286</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>288</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>290</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>291</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>292</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>293</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>294</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>295</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>296</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>297</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>298</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>299</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>300</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>301</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>302</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>303</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>304</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F5" t="s">
-        <v>248</v>
-      </c>
-      <c r="G5" t="s">
-        <v>249</v>
-      </c>
-      <c r="H5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K5" t="s">
-        <v>251</v>
-      </c>
-      <c r="L5" t="s">
-        <v>252</v>
-      </c>
-      <c r="N5" t="s">
-        <v>253</v>
-      </c>
-      <c r="P5" t="s">
-        <v>254</v>
-      </c>
-      <c r="R5" t="s">
-        <v>255</v>
-      </c>
-      <c r="T5" t="s">
-        <v>256</v>
-      </c>
-      <c r="U5" t="s">
-        <v>257</v>
-      </c>
-      <c r="V5" t="s">
-        <v>258</v>
-      </c>
-      <c r="W5" t="s">
-        <v>259</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>260</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>261</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>263</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>264</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>265</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>266</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>268</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>269</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>270</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>271</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>272</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>273</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>274</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>275</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>276</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>277</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>278</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>279</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>280</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>281</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>282</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>283</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>284</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>285</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>286</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>287</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>288</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>289</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>290</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>291</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>292</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>293</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>294</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>295</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>296</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>297</v>
-      </c>
-      <c r="BZ5" t="s">
-        <v>298</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>299</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>300</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>301</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>302</v>
-      </c>
-      <c r="CF5" t="s">
-        <v>303</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>304</v>
-      </c>
-      <c r="CH5" t="s">
+    <row r="6" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>305</v>
       </c>
+      <c r="D6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F6" t="s">
+        <v>307</v>
+      </c>
+      <c r="G6" t="s">
+        <v>308</v>
+      </c>
+      <c r="H6" t="s">
+        <v>309</v>
+      </c>
+      <c r="K6" t="s">
+        <v>310</v>
+      </c>
+      <c r="L6" t="s">
+        <v>311</v>
+      </c>
+      <c r="N6" t="s">
+        <v>312</v>
+      </c>
+      <c r="P6" t="s">
+        <v>313</v>
+      </c>
+      <c r="T6" t="s">
+        <v>314</v>
+      </c>
+      <c r="V6" t="s">
+        <v>315</v>
+      </c>
+      <c r="W6" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>317</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>319</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>320</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>321</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>322</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>323</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>325</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>326</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>328</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>329</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>330</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>331</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>332</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>333</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>334</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>335</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>336</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>337</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>338</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>339</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>340</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>341</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>342</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>343</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>344</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>345</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>346</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>347</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>348</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>349</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>350</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>351</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>352</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>353</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>354</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>306</v>
-      </c>
-      <c r="D6" t="s">
-        <v>307</v>
-      </c>
-      <c r="F6" t="s">
-        <v>308</v>
-      </c>
-      <c r="G6" t="s">
-        <v>309</v>
-      </c>
-      <c r="H6" t="s">
-        <v>310</v>
-      </c>
-      <c r="K6" t="s">
-        <v>311</v>
-      </c>
-      <c r="L6" t="s">
-        <v>312</v>
-      </c>
-      <c r="N6" t="s">
-        <v>313</v>
-      </c>
-      <c r="P6" t="s">
-        <v>314</v>
-      </c>
-      <c r="T6" t="s">
-        <v>315</v>
-      </c>
-      <c r="V6" t="s">
-        <v>316</v>
-      </c>
-      <c r="W6" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>319</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>320</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>321</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>322</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>323</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>324</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>325</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>326</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>327</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>328</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>329</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>330</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>331</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>332</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>333</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>334</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>335</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>336</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>337</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>338</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>339</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>340</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>341</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>342</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>343</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>344</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>345</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>346</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>347</v>
-      </c>
-      <c r="BY6" t="s">
+    <row r="7" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F7" t="s">
+        <v>357</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>359</v>
+      </c>
+      <c r="K7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L7" t="s">
+        <v>361</v>
+      </c>
+      <c r="N7" t="s">
         <v>348</v>
       </c>
-      <c r="BZ6" t="s">
-        <v>349</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>350</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>351</v>
-      </c>
-      <c r="CC6" t="s">
-        <v>352</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>353</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>354</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>355</v>
+      <c r="P7" t="s">
+        <v>362</v>
+      </c>
+      <c r="T7" t="s">
+        <v>363</v>
+      </c>
+      <c r="V7" t="s">
+        <v>364</v>
+      </c>
+      <c r="W7" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>366</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>368</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>370</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>371</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>374</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>375</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>376</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>377</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>378</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>379</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>380</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>381</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>382</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>383</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>384</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>385</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>386</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>387</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>388</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>389</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>390</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>391</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>392</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>393</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>394</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>395</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>396</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>397</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>398</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>399</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>356</v>
-      </c>
-      <c r="D7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F7" t="s">
-        <v>358</v>
-      </c>
-      <c r="G7" t="s">
-        <v>359</v>
-      </c>
-      <c r="H7" t="s">
-        <v>360</v>
-      </c>
-      <c r="K7" t="s">
-        <v>361</v>
-      </c>
-      <c r="L7" t="s">
-        <v>362</v>
-      </c>
-      <c r="N7" t="s">
-        <v>349</v>
-      </c>
-      <c r="P7" t="s">
-        <v>363</v>
-      </c>
-      <c r="T7" t="s">
-        <v>364</v>
-      </c>
-      <c r="V7" t="s">
-        <v>365</v>
-      </c>
-      <c r="W7" t="s">
-        <v>366</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>367</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>368</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>369</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>370</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>371</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>372</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>373</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>374</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>375</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>376</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>378</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>379</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>380</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>381</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>382</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>383</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>384</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>385</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>386</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>387</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>388</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>389</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>390</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>391</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>392</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>393</v>
-      </c>
-      <c r="BZ7" t="s">
-        <v>394</v>
-      </c>
-      <c r="CA7" t="s">
-        <v>395</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>396</v>
-      </c>
-      <c r="CC7" t="s">
-        <v>397</v>
-      </c>
-      <c r="CF7" t="s">
-        <v>398</v>
-      </c>
-      <c r="CG7" t="s">
-        <v>399</v>
-      </c>
-      <c r="CH7" t="s">
+    <row r="8" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>400</v>
       </c>
+      <c r="D8" t="s">
+        <v>401</v>
+      </c>
+      <c r="F8" t="s">
+        <v>402</v>
+      </c>
+      <c r="G8" t="s">
+        <v>403</v>
+      </c>
+      <c r="H8" t="s">
+        <v>404</v>
+      </c>
+      <c r="K8" t="s">
+        <v>405</v>
+      </c>
+      <c r="L8" t="s">
+        <v>406</v>
+      </c>
+      <c r="V8" t="s">
+        <v>407</v>
+      </c>
+      <c r="W8" t="s">
+        <v>408</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>410</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>411</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>413</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>414</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>415</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>416</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>417</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>418</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>419</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>420</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>421</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>422</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>423</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>424</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>425</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>426</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>427</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>428</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>429</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>430</v>
+      </c>
+      <c r="CF8" t="s">
+        <v>431</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>432</v>
+      </c>
+      <c r="CH8" t="s">
+        <v>433</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:86" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>401</v>
-      </c>
-      <c r="D8" t="s">
-        <v>402</v>
-      </c>
-      <c r="F8" t="s">
-        <v>403</v>
-      </c>
-      <c r="G8" t="s">
-        <v>404</v>
-      </c>
-      <c r="H8" t="s">
-        <v>405</v>
-      </c>
-      <c r="K8" t="s">
-        <v>406</v>
-      </c>
-      <c r="L8" t="s">
-        <v>407</v>
-      </c>
-      <c r="V8" t="s">
-        <v>408</v>
-      </c>
-      <c r="W8" t="s">
-        <v>409</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>410</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>411</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>412</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>413</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>414</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>415</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>416</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>417</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>418</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>419</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>420</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>421</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>422</v>
-      </c>
-      <c r="BK8" t="s">
-        <v>423</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>424</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>425</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>426</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>427</v>
-      </c>
-      <c r="BZ8" t="s">
-        <v>428</v>
-      </c>
-      <c r="CA8" t="s">
-        <v>429</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>430</v>
-      </c>
-      <c r="CC8" t="s">
-        <v>431</v>
-      </c>
-      <c r="CF8" t="s">
-        <v>432</v>
-      </c>
-      <c r="CG8" t="s">
-        <v>433</v>
-      </c>
-      <c r="CH8" t="s">
+    <row r="9" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
         <v>434</v>
       </c>
+      <c r="L9" t="s">
+        <v>435</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>436</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>437</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>438</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>439</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>440</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>441</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>442</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>443</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>444</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>445</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>446</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
-        <v>435</v>
-      </c>
-      <c r="L9" t="s">
-        <v>436</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>437</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>438</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>439</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>440</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>441</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>442</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>443</v>
-      </c>
-      <c r="BZ9" t="s">
-        <v>444</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>445</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>446</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -11665,122 +11664,122 @@
     <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="6">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>289</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="63" t="s">
+        <v>448</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="7">
         <f>C1*4</f>
         <v>1156</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" s="9">
+        <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
+        <v>1152</v>
+      </c>
+      <c r="E3" s="65" t="s">
         <v>449</v>
       </c>
-      <c r="B3" s="13">
-        <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>1156</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="B4" s="16">
+      <c r="B4" s="11">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <f>AHL!I1</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
+        <v>451</v>
+      </c>
+      <c r="F4" t="s">
         <v>452</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>453</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>454</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>455</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>456</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>457</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>458</v>
       </c>
-      <c r="L4" t="s">
-        <v>459</v>
-      </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="11">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>33</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="F5" s="18">
+      <c r="E5" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="F5" s="13">
         <v>2</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="14">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="15">
         <f>B4/B3</f>
-        <v>0.14619377162629757</v>
-      </c>
-      <c r="I5" s="21">
+        <v>0.14496527777777779</v>
+      </c>
+      <c r="I5" s="16">
         <f>C2*G5</f>
         <v>177.84615384615387</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>169</v>
-      </c>
-      <c r="K5" s="22">
+        <v>167</v>
+      </c>
+      <c r="K5" s="17">
         <f>J5-I5</f>
-        <v>-8.846153846153868</v>
-      </c>
-      <c r="L5" s="23">
+        <v>-10.846153846153868</v>
+      </c>
+      <c r="L5" s="18">
         <f>K5/4</f>
-        <v>-2.211538461538467</v>
+        <v>-2.711538461538467</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="11">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
         <v>456</v>
       </c>
@@ -11788,445 +11787,445 @@
         <f>AHL!X1</f>
         <v>8</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="13">
         <v>1</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="14">
         <f>F6/13</f>
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="H6" s="20">
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="H6" s="15">
         <f>B5/B3</f>
-        <v>0.028546712802768166</v>
-      </c>
-      <c r="I6" s="21">
+        <v>2.8645833333333332E-2</v>
+      </c>
+      <c r="I6" s="16">
         <f>C2*G6</f>
-        <v>88.92307692307693</v>
+        <v>88.923076923076934</v>
       </c>
       <c r="J6">
         <f>B5</f>
         <v>33</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="17">
         <f>J6-I6</f>
         <v>-55.923076923076934</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="18">
         <f t="shared" ref="L6" si="0">K6/4</f>
         <v>-13.980769230769234</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="20">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C7">
         <f>SUM(AHL!AL1,AHL!AU1,AHL!BA1,AHL!BD1,AHL!BE1,AHL!BF1,AHL!BG1,AHL!BM1)</f>
-        <v>127</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="F7" s="27">
+        <v>126</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="F7" s="22">
         <v>3</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="23">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="24">
         <f>(B5+B4)/B3</f>
-        <v>0.17474048442906576</v>
-      </c>
-      <c r="I7" s="21">
+        <v>0.1736111111111111</v>
+      </c>
+      <c r="I7" s="16">
         <f>C2*G7</f>
-        <v>266.7692307692308</v>
+        <v>266.76923076923077</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>202</v>
-      </c>
-      <c r="K7" s="22">
+        <v>200</v>
+      </c>
+      <c r="K7" s="17">
         <f>J7-I7</f>
-        <v>-64.76923076923077</v>
-      </c>
-      <c r="L7" s="23">
+        <v>-66.769230769230774</v>
+      </c>
+      <c r="L7" s="18">
         <f>K7/4</f>
-        <v>-16.192307692307693</v>
+        <v>-16.692307692307693</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
-        <v>461</v>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>460</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
-        <v>158</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="F8" s="32">
+        <v>156</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>461</v>
+      </c>
+      <c r="F8" s="27">
         <v>6</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="28">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="29">
         <f>B6/B3</f>
-        <v>0.3944636678200692</v>
-      </c>
-      <c r="I8" s="21">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="I8" s="16">
         <f>C2*G8</f>
-        <v>533.5384615384615</v>
+        <v>533.53846153846155</v>
       </c>
       <c r="J8">
         <f>B6</f>
         <v>456</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="17">
         <f>J8-I8</f>
-        <v>-77.53846153846155</v>
-      </c>
-      <c r="L8" s="23">
+        <v>-77.538461538461547</v>
+      </c>
+      <c r="L8" s="18">
         <f>K8/4</f>
         <v>-19.384615384615387</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>1156</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>464</v>
-      </c>
-      <c r="F9" s="32">
+        <v>1152</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>463</v>
+      </c>
+      <c r="F9" s="27">
         <v>4</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="28">
         <f t="shared" si="1"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H9" s="34">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H9" s="29">
         <f>B7/B3</f>
-        <v>0.43079584775086505</v>
-      </c>
-      <c r="I9" s="21">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="I9" s="16">
         <f>C2*G9</f>
         <v>355.69230769230774</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>498</v>
-      </c>
-      <c r="K9" s="35">
+        <v>496</v>
+      </c>
+      <c r="K9" s="30">
         <f>J9-I9</f>
-        <v>142.30769230769226</v>
-      </c>
-      <c r="L9" s="23">
+        <v>140.30769230769226</v>
+      </c>
+      <c r="L9" s="18">
         <f>K9/4</f>
-        <v>35.576923076923066</v>
+        <v>35.076923076923066</v>
       </c>
     </row>
-    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="36" t="s">
-        <v>465</v>
-      </c>
-      <c r="I11" s="37">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="I11" s="32">
         <f>SUM(I7:I9)</f>
         <v>1156</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="26">
         <f>SUM(J7:J9)</f>
-        <v>1156</v>
-      </c>
-      <c r="K11" s="38">
+        <v>1152</v>
+      </c>
+      <c r="K11" s="33">
         <f>SUM(K7:K9)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="39">
+        <v>-4.0000000000000568</v>
+      </c>
+      <c r="L11" s="34">
         <f>SUM(L7:L9)</f>
-        <v>0</v>
+        <v>-1.0000000000000142</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
+        <v>465</v>
+      </c>
+      <c r="F16" t="s">
+        <v>452</v>
+      </c>
+      <c r="G16" t="s">
         <v>466</v>
       </c>
-      <c r="F16" t="s">
-        <v>453</v>
-      </c>
-      <c r="G16" t="s">
-        <v>467</v>
-      </c>
       <c r="H16" t="s">
+        <v>454</v>
+      </c>
+      <c r="I16" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="J16" s="35" t="s">
         <v>456</v>
       </c>
-      <c r="J16" s="40" t="s">
+      <c r="K16" t="s">
         <v>457</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>458</v>
       </c>
-      <c r="L16" t="s">
+    </row>
+    <row r="17" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E17" s="36" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="41" t="s">
-        <v>460</v>
-      </c>
-      <c r="F17" s="42">
+      <c r="F17" s="37">
         <v>3</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="38">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="39">
         <f>(B5+B4)/B3</f>
-        <v>0.17474048442906576</v>
-      </c>
-      <c r="I17" s="45">
+        <v>0.1736111111111111</v>
+      </c>
+      <c r="I17" s="40">
         <f>B3*G17</f>
-        <v>266.7692307692308</v>
-      </c>
-      <c r="J17" s="46">
+        <v>265.84615384615387</v>
+      </c>
+      <c r="J17" s="41">
         <f>B5+B4</f>
-        <v>202</v>
-      </c>
-      <c r="K17" s="47">
+        <v>200</v>
+      </c>
+      <c r="K17" s="42">
         <f>J17-I17</f>
-        <v>-64.76923076923077</v>
-      </c>
-      <c r="L17" s="23">
+        <v>-65.846153846153868</v>
+      </c>
+      <c r="L17" s="18">
         <f>K17/4</f>
-        <v>-16.192307692307693</v>
+        <v>-16.461538461538467</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="48" t="s">
-        <v>462</v>
-      </c>
-      <c r="F18" s="49">
+      <c r="E18" s="43" t="s">
+        <v>461</v>
+      </c>
+      <c r="F18" s="44">
         <v>6</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="45">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="51">
+      <c r="H18" s="46">
         <f>B6/B3</f>
-        <v>0.3944636678200692</v>
-      </c>
-      <c r="I18" s="52">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="I18" s="47">
         <f>B3*G18</f>
-        <v>533.5384615384615</v>
-      </c>
-      <c r="J18" s="53">
+        <v>531.69230769230774</v>
+      </c>
+      <c r="J18" s="48">
         <f>B6</f>
         <v>456</v>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="49">
         <f>J18-I18</f>
-        <v>-77.53846153846155</v>
-      </c>
-      <c r="L18" s="23">
+        <v>-75.692307692307736</v>
+      </c>
+      <c r="L18" s="18">
         <f>K18/4</f>
-        <v>-19.384615384615387</v>
-      </c>
-      <c r="Q18" s="55"/>
+        <v>-18.923076923076934</v>
+      </c>
+      <c r="Q18" s="50"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="56" t="s">
-        <v>464</v>
-      </c>
-      <c r="F19" s="57">
+    <row r="19" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="51" t="s">
+        <v>463</v>
+      </c>
+      <c r="F19" s="52">
         <v>4</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="53">
         <f t="shared" si="2"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H19" s="59">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H19" s="54">
         <f>B7/B3</f>
-        <v>0.43079584775086505</v>
-      </c>
-      <c r="I19" s="60">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="I19" s="55">
         <f>B3*G19</f>
-        <v>355.69230769230774</v>
-      </c>
-      <c r="J19" s="61">
+        <v>354.46153846153845</v>
+      </c>
+      <c r="J19" s="56">
         <f>B7</f>
-        <v>498</v>
-      </c>
-      <c r="K19" s="62">
+        <v>496</v>
+      </c>
+      <c r="K19" s="57">
         <f>J19-I19</f>
-        <v>142.30769230769226</v>
-      </c>
-      <c r="L19" s="23">
+        <v>141.53846153846155</v>
+      </c>
+      <c r="L19" s="18">
         <f>K19/4</f>
-        <v>35.576923076923066</v>
+        <v>35.384615384615387</v>
       </c>
     </row>
-    <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E21" s="63" t="s">
-        <v>468</v>
-      </c>
-      <c r="F21" s="63"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="63"/>
+    <row r="21" spans="5:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E21" s="66" t="s">
+        <v>467</v>
+      </c>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G22" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H22" t="s">
+        <v>454</v>
+      </c>
+      <c r="I22" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="J22" s="35" t="s">
         <v>456</v>
       </c>
-      <c r="J22" s="40" t="s">
+      <c r="K22" t="s">
         <v>457</v>
       </c>
-      <c r="K22" t="s">
-        <v>458</v>
-      </c>
     </row>
-    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E23" s="41" t="s">
-        <v>460</v>
-      </c>
-      <c r="F23" s="42">
+    <row r="23" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E23" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="F23" s="37">
         <v>3</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="38">
         <f t="shared" ref="G23:G25" si="3">F23/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H23" s="44">
+      <c r="H23" s="39">
         <f>(B4+B5-C4)/(B3-C8)</f>
-        <v>0.17935871743486975</v>
-      </c>
-      <c r="I23" s="45">
+        <v>0.17871485943775101</v>
+      </c>
+      <c r="I23" s="40">
         <f>(B3-C8) *G23</f>
-        <v>230.30769230769232</v>
-      </c>
-      <c r="J23" s="46">
+        <v>229.84615384615387</v>
+      </c>
+      <c r="J23" s="41">
         <f>B4+B5-C4</f>
-        <v>179</v>
-      </c>
-      <c r="K23" s="47">
+        <v>178</v>
+      </c>
+      <c r="K23" s="42">
         <f>J23-I23</f>
-        <v>-51.30769230769232</v>
+        <v>-51.846153846153868</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E24" s="48" t="s">
-        <v>462</v>
-      </c>
-      <c r="F24" s="49">
+    <row r="24" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="43" t="s">
+        <v>461</v>
+      </c>
+      <c r="F24" s="44">
         <v>6</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="45">
         <f t="shared" si="3"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H24" s="51">
+      <c r="H24" s="46">
         <f>(B6-C4)/(B3-C8)</f>
-        <v>0.4338677354709419</v>
-      </c>
-      <c r="I24" s="52">
+        <v>0.43574297188755018</v>
+      </c>
+      <c r="I24" s="47">
         <f>(B3-C8)*G24</f>
-        <v>460.61538461538464</v>
-      </c>
-      <c r="J24" s="53">
+        <v>459.69230769230774</v>
+      </c>
+      <c r="J24" s="48">
         <f>B6-C6</f>
         <v>448</v>
       </c>
-      <c r="K24" s="54">
+      <c r="K24" s="49">
         <f>J24-I24</f>
-        <v>-12.615384615384642</v>
+        <v>-11.692307692307736</v>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E25" s="56" t="s">
-        <v>464</v>
-      </c>
-      <c r="F25" s="57">
+    <row r="25" spans="5:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="51" t="s">
+        <v>463</v>
+      </c>
+      <c r="F25" s="52">
         <v>4</v>
       </c>
-      <c r="G25" s="58">
+      <c r="G25" s="53">
         <f t="shared" si="3"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H25" s="59">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H25" s="54">
         <f>(B7-C7)/(B3-C8)</f>
-        <v>0.3717434869739479</v>
-      </c>
-      <c r="I25" s="60">
+        <v>0.37148594377510041</v>
+      </c>
+      <c r="I25" s="55">
         <f>(B3-C8)*G25</f>
-        <v>307.0769230769231</v>
-      </c>
-      <c r="J25" s="61">
+        <v>306.46153846153845</v>
+      </c>
+      <c r="J25" s="56">
         <f>B7-C7</f>
-        <v>371</v>
-      </c>
-      <c r="K25" s="62">
+        <v>370</v>
+      </c>
+      <c r="K25" s="57">
         <f>J25-I25</f>
-        <v>63.923076923076906</v>
+        <v>63.538461538461547</v>
       </c>
     </row>
-    <row r="26" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E26" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="64">
+      <c r="H26" s="58">
         <f>C8/B9</f>
-        <v>0.13667820069204153</v>
+        <v>0.13541666666666666</v>
       </c>
       <c r="I26" s="5"/>
-      <c r="J26" s="65">
+      <c r="J26" s="59">
         <f>C8</f>
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K26" s="5"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J28">
         <f>SUM(J23:J26)</f>
-        <v>1156</v>
-      </c>
-      <c r="K28" s="66">
+        <v>1152</v>
+      </c>
+      <c r="K28" s="60">
         <f>SUM(K23:K25)</f>
-        <v>-5.684341886080802e-14</v>
+        <v>-5.6843418860808015E-14</v>
       </c>
     </row>
   </sheetData>
